--- a/data/trans_orig/IP22_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP22_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21059</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35930</t>
+          <t>36284</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33078</t>
+          <t>34285</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42408</t>
+          <t>42693</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63555</t>
+          <t>63912</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102796</t>
+          <t>102442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>117667</t>
+          <t>118124</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>119999</t>
+          <t>118792</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134540</t>
+          <t>133750</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228248</t>
+          <t>227891</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249395</t>
+          <t>249110</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>31693</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>48748</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46707</t>
+          <t>46217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67600</t>
+          <t>65940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84205</t>
+          <t>82722</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111381</t>
+          <t>110499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147112</t>
+          <t>146415</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163887</t>
+          <t>163470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144542</t>
+          <t>146202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>165435</t>
+          <t>165925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295924</t>
+          <t>296806</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>323100</t>
+          <t>324583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,69%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28736</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44789</t>
+          <t>45871</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31541</t>
+          <t>31359</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49288</t>
+          <t>47981</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63232</t>
+          <t>64046</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87917</t>
+          <t>88315</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93028</t>
+          <t>91946</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109081</t>
+          <t>108670</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100369</t>
+          <t>101676</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118116</t>
+          <t>118298</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>199557</t>
+          <t>199159</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>224242</t>
+          <t>223428</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37825</t>
+          <t>36772</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44604</t>
+          <t>44403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52409</t>
+          <t>50307</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76206</t>
+          <t>75475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171490</t>
+          <t>172543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189264</t>
+          <t>189411</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163220</t>
+          <t>163421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180485</t>
+          <t>181042</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340933</t>
+          <t>341664</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364730</t>
+          <t>366832</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>114820</t>
+          <t>114811</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>148284</t>
+          <t>148370</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139843</t>
+          <t>140014</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>175288</t>
+          <t>175099</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264539</t>
+          <t>264161</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>311881</t>
+          <t>315664</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>532737</t>
+          <t>532651</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>566201</t>
+          <t>566210</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>547412</t>
+          <t>547601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>582857</t>
+          <t>582686</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1091840</t>
+          <t>1088057</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1139182</t>
+          <t>1139560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24437</t>
+          <t>24399</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40584</t>
+          <t>41956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28969</t>
+          <t>29494</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48969</t>
+          <t>48092</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58099</t>
+          <t>58713</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83192</t>
+          <t>84012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98773</t>
+          <t>97401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114920</t>
+          <t>114958</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105715</t>
+          <t>106592</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125715</t>
+          <t>125190</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>210849</t>
+          <t>210029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>235942</t>
+          <t>235328</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,03%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50060</t>
+          <t>49646</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70461</t>
+          <t>70739</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51123</t>
+          <t>49972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73057</t>
+          <t>72469</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>105593</t>
+          <t>105879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136945</t>
+          <t>136846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135252</t>
+          <t>134974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155653</t>
+          <t>156067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150109</t>
+          <t>150697</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172043</t>
+          <t>173194</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>291934</t>
+          <t>292033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>323286</t>
+          <t>323000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25023</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41584</t>
+          <t>40629</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51163</t>
+          <t>50829</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71380</t>
+          <t>71109</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80692</t>
+          <t>82261</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107296</t>
+          <t>107288</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113792</t>
+          <t>114747</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130353</t>
+          <t>130436</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93467</t>
+          <t>93738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113684</t>
+          <t>114018</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212927</t>
+          <t>212935</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>239531</t>
+          <t>237962</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32513</t>
+          <t>33388</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52480</t>
+          <t>53617</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36546</t>
+          <t>36051</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55646</t>
+          <t>56868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73648</t>
+          <t>74215</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>104228</t>
+          <t>103016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157820</t>
+          <t>156683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177787</t>
+          <t>176912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152008</t>
+          <t>150786</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171108</t>
+          <t>171603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>313726</t>
+          <t>314938</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>344306</t>
+          <t>343739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>149607</t>
+          <t>148063</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187162</t>
+          <t>187006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187350</t>
+          <t>186934</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>228833</t>
+          <t>227835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>346823</t>
+          <t>348333</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>404113</t>
+          <t>403716</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>523584</t>
+          <t>523740</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>561139</t>
+          <t>562683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>521519</t>
+          <t>522517</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>563002</t>
+          <t>563418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1056984</t>
+          <t>1057381</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1114274</t>
+          <t>1112764</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19365</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35009</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>18576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35207</t>
+          <t>36042</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42126</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65203</t>
+          <t>65433</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>98771</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114342</t>
+          <t>113940</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112869</t>
+          <t>112034</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129487</t>
+          <t>129500</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>216580</t>
+          <t>216350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239657</t>
+          <t>238673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,7%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>30329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47737</t>
+          <t>47998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26409</t>
+          <t>27917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44570</t>
+          <t>44761</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62532</t>
+          <t>62296</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87109</t>
+          <t>87699</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159510</t>
+          <t>159249</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>177039</t>
+          <t>176918</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179789</t>
+          <t>179598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>197950</t>
+          <t>196442</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344497</t>
+          <t>343907</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>369074</t>
+          <t>369310</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26368</t>
+          <t>26755</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42755</t>
+          <t>43757</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>24704</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40728</t>
+          <t>41257</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56173</t>
+          <t>56637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78044</t>
+          <t>79168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113242</t>
+          <t>112240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129629</t>
+          <t>129242</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125945</t>
+          <t>125416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142313</t>
+          <t>141969</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244626</t>
+          <t>243502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>266497</t>
+          <t>266033</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17300</t>
+          <t>17466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33346</t>
+          <t>33021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22358</t>
+          <t>22595</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39806</t>
+          <t>39849</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44505</t>
+          <t>44603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67884</t>
+          <t>68297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174074</t>
+          <t>174399</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190120</t>
+          <t>189954</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165112</t>
+          <t>165069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>182560</t>
+          <t>182323</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344454</t>
+          <t>344041</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>367833</t>
+          <t>367735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,18%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109625</t>
+          <t>108595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>143203</t>
+          <t>140126</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108303</t>
+          <t>108277</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142659</t>
+          <t>141691</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227897</t>
+          <t>224244</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273282</t>
+          <t>271598</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>561168</t>
+          <t>564245</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>594746</t>
+          <t>595776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>601367</t>
+          <t>602335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>635723</t>
+          <t>635749</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1175115</t>
+          <t>1176799</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1220500</t>
+          <t>1224153</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28170</t>
+          <t>28001</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>13643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31830</t>
+          <t>31505</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31947</t>
+          <t>31820</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54210</t>
+          <t>53279</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89110</t>
+          <t>89279</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102476</t>
+          <t>102502</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108582</t>
+          <t>108907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127125</t>
+          <t>126769</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>203483</t>
+          <t>204414</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>225746</t>
+          <t>225873</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28293</t>
+          <t>27956</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55319</t>
+          <t>54180</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24860</t>
+          <t>24494</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44677</t>
+          <t>44119</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57744</t>
+          <t>57640</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91167</t>
+          <t>91041</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135193</t>
+          <t>136332</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>162219</t>
+          <t>162556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210358</t>
+          <t>210916</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>230175</t>
+          <t>230541</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354381</t>
+          <t>354507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>387804</t>
+          <t>387908</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,06%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15721</t>
+          <t>16483</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38102</t>
+          <t>37637</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18933</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38164</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40378</t>
+          <t>39671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68829</t>
+          <t>70361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151483</t>
+          <t>151948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>173864</t>
+          <t>173102</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147122</t>
+          <t>146912</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166353</t>
+          <t>165966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>306042</t>
+          <t>304510</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>334493</t>
+          <t>335200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,42%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>12154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28040</t>
+          <t>26729</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26592</t>
+          <t>26417</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45457</t>
+          <t>45578</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40824</t>
+          <t>41645</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67341</t>
+          <t>65332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139199</t>
+          <t>140510</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>155220</t>
+          <t>155085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135781</t>
+          <t>135660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154646</t>
+          <t>154821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281136</t>
+          <t>283145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>307653</t>
+          <t>306832</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84455</t>
+          <t>84008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123880</t>
+          <t>124638</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99644</t>
+          <t>99617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138030</t>
+          <t>135313</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>196171</t>
+          <t>194422</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>251523</t>
+          <t>251730</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>540737</t>
+          <t>539979</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>580162</t>
+          <t>580609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>623942</t>
+          <t>626659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>662328</t>
+          <t>662355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1175066</t>
+          <t>1174859</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1230418</t>
+          <t>1232167</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,37%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP22_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25561</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19013</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33631</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>27747</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20602</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36284</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20663</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>36045</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>20,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>25561</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>19327</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>34285</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42693</t>
+          <t>42865</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63912</t>
+          <t>64858</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>127516</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>119446</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>134064</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,3%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,03%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>110979</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>102442</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>118124</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>102681</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>118063</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>80,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>73,84%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>85,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>127516</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>118792</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>133750</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>83,3%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>227891</t>
+          <t>226945</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249110</t>
+          <t>248938</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56672</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>46159</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>66731</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>21,76%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>31,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>39951</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>31693</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>48748</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>31338</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>49068</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>20,47%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,24%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,98%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>56672</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>46217</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>65940</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>26,71%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82722</t>
+          <t>83301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110499</t>
+          <t>110255</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>155470</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>145411</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>165983</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>73,29%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>78,24%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>155212</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>146415</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>163470</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>146095</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>163825</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>79,53%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>155470</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>146202</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>165925</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>73,29%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296806</t>
+          <t>297050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>324583</t>
+          <t>324004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,55%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1414,67 +1414,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>39478</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31020</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>48545</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>26,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>32,44%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>36008</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29147</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>45871</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>28441</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>43934</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>26,13%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>39478</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>31359</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>47981</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>26,38%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64046</t>
+          <t>65030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88315</t>
+          <t>87265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>110179</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>101112</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>118637</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>73,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>67,56%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>79,27%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>101809</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>91946</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>108670</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>93883</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>109376</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>73,87%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>66,72%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>78,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>110179</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>101676</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>118298</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>73,62%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>199159</t>
+          <t>200209</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>223428</t>
+          <t>222444</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,38%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>35318</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27561</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>44922</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>27955</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19904</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36772</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>20085</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>37329</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,36%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>35318</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>26782</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>44403</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,99%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50307</t>
+          <t>52690</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75475</t>
+          <t>75923</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>172506</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>162902</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>180263</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,01%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>78,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>181360</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>172543</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>189411</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>171986</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>189230</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,64%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,49%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>172506</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>163421</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>181042</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,01%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341664</t>
+          <t>341216</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>366832</t>
+          <t>364449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,37%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>157029</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>138749</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>177154</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>21,73%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>19,2%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>131661</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>114811</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>148370</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>116201</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>149172</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>19,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>157029</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>140014</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>175099</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264161</t>
+          <t>263954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>315664</t>
+          <t>313393</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>565671</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>545546</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>583951</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>78,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>75,49%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>80,8%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>817</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>549360</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>532651</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>566210</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>531849</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>564820</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>80,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>78,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>83,14%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>565671</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>547601</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>582686</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>78,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1088057</t>
+          <t>1090328</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1139560</t>
+          <t>1139767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,2%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38472</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29804</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>48445</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>32719</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24399</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>41956</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>24566</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>43184</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>23,48%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>38472</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>29494</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>48092</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>24,87%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58713</t>
+          <t>58844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84012</t>
+          <t>83545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>116212</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>106239</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>124880</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>75,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>80,73%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>106638</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>97401</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>114958</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>96173</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>114791</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>76,52%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>69,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,49%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>116212</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>106592</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>125190</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>75,13%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>210029</t>
+          <t>210496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>235328</t>
+          <t>235197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>61684</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>49460</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>72932</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>32,68%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>59736</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>49646</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>70739</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>50523</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>70812</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>29,04%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24,13%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,39%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>61684</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>49972</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>72469</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>27,64%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>105879</t>
+          <t>105721</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136846</t>
+          <t>136694</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>161482</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>150234</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>173706</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>67,32%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>77,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>145977</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>134974</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>156067</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>134901</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>155190</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>70,96%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,87%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>161482</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>150697</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>173194</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>72,36%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>292033</t>
+          <t>292185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>323000</t>
+          <t>323158</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,35%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223166</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223166</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223166</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>318</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223166</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223166</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223166</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>60934</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>51325</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>70692</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>36,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>31,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42,88%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>32862</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24940</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>40629</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>24526</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>40985</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21,15%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>60934</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>50829</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>71109</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>36,96%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82261</t>
+          <t>81977</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107288</t>
+          <t>107808</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>103913</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>94155</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>113522</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>63,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>57,12%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>68,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>122514</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>114747</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>130436</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>114391</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>130850</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>78,85%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>73,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>83,95%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>103913</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>93738</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>114018</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>63,04%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212935</t>
+          <t>212415</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>237962</t>
+          <t>238246</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,4%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>164847</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>164847</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>164847</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>164847</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>164847</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>164847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>45727</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36187</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>55146</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,02%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>42501</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>33388</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>53617</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>34007</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>54457</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>20,21%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,88%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25,5%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>45727</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>36051</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>56868</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>22,02%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74215</t>
+          <t>74613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103016</t>
+          <t>104073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>161927</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>152508</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>171467</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>77,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>82,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>167799</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>156683</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>176912</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>155843</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>176293</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>79,79%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>74,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,12%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>161927</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>150786</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>171603</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>77,98%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314938</t>
+          <t>313881</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>343739</t>
+          <t>343341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207654</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207654</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207654</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207654</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207654</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207654</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>206817</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>187656</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>230418</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>27,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25,01%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>30,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>167818</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>148063</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>187006</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>151095</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>186466</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>23,61%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20,83%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>206817</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>186934</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>227835</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>27,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>348333</t>
+          <t>349557</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>403716</t>
+          <t>404110</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>543535</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>519934</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>562696</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>72,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>69,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>74,99%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>781</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>542928</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>523740</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>562683</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>524280</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>559651</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>76,39%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>73,69%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>79,17%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>543535</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>522517</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>563418</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>72,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1057381</t>
+          <t>1056987</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1112764</t>
+          <t>1111540</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>750352</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>750352</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>750352</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>710746</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>710746</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>710746</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>750352</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>750352</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>750352</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19151</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35371</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>26664</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19767</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34936</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19504</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>34190</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>19,94%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>26370</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>18576</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>36042</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>42994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65433</t>
+          <t>64434</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121706</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>112705</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>128925</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>107043</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>98771</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>113940</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>99517</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>114203</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>80,06%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>85,22%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>121706</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>112034</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>129500</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>82,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>216350</t>
+          <t>217349</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>238673</t>
+          <t>238789</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,74%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>35250</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27690</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>44502</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>38477</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30329</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>47998</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>30244</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>47452</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>18,57%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14,63%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,16%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>35250</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>27917</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>44761</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>15,71%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62296</t>
+          <t>60771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87699</t>
+          <t>87068</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>189109</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>179857</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>196669</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,29%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>168770</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>159249</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>176918</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>159795</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>177003</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>81,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>189109</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>179598</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>196442</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>84,29%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>343907</t>
+          <t>344538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>369310</t>
+          <t>370835</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,92%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32409</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25105</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41229</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>34286</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26755</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>43757</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>26866</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42503</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21,98%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>32409</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>24704</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>41257</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56637</t>
+          <t>55718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79168</t>
+          <t>79646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>134264</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>125444</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>141568</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>80,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,94%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>121711</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>112240</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>129242</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>113494</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>129131</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>78,02%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>71,95%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>82,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>134264</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>125416</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>141969</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>80,56%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>243502</t>
+          <t>243024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>266033</t>
+          <t>266952</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,73%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30499</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22232</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>39551</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>24657</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17466</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33021</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18075</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33239</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,89%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>30499</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>22595</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>39849</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44603</t>
+          <t>43608</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68297</t>
+          <t>66073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>174419</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>165367</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>182686</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,7%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>182763</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>174399</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>189954</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>174181</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>189345</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,11%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>174419</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>165069</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>182323</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,12%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344041</t>
+          <t>346265</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>367735</t>
+          <t>368730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,42%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204918</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204918</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204918</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204918</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204918</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204918</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>124527</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>107955</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>142338</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19,13%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>124084</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>108595</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>140126</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>108859</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>140183</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>17,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,42%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>124527</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>108277</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>141691</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>224244</t>
+          <t>226452</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>271598</t>
+          <t>272633</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>619499</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>601688</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>636071</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>80,87%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>867</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>580287</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>564245</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>595776</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>564188</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>595512</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>82,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>80,11%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>84,58%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>886</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>619499</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>602335</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>635749</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>83,26%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1176799</t>
+          <t>1175764</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1224153</t>
+          <t>1221945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744026</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744026</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744026</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744026</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744026</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744026</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18813</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12469</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27896</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>20629</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14778</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>28001</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>20267</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31505</t>
+          <t>28048</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>41797</t>
+          <t>39080</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31820</t>
+          <t>29558</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53279</t>
+          <t>50728</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>107093</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>98010</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>113437</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>85,06%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>90,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>96651</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>89279</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>102502</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,13%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,4%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>119243</t>
+          <t>100804</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108907</t>
+          <t>93023</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126769</t>
+          <t>106805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>215896</t>
+          <t>207897</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204414</t>
+          <t>196249</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>225873</t>
+          <t>217419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>88,03%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,107 +6907,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>30355</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22633</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41294</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,54%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>37667</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>27956</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54180</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>19,77%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>31481</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>23159</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>40591</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>17,07%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>12,56%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>22,01%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>61836</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>49412</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>75640</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>14,67%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>33358</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>24494</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>44119</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>17,3%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>71024</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>57640</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>91041</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>15,94%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -7020,107 +7020,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>206851</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>195912</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>214573</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,46%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>152845</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>136332</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>162556</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>80,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>152932</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>143822</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>161254</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>82,93%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>77,99%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>87,44%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>359783</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>345979</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>372207</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>85,33%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>221677</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>210916</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>230541</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>86,92%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>82,7%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>90,4%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>374524</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>354507</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>387908</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>84,06%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25337</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17646</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35882</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>26895</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16483</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>37637</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27674</t>
+          <t>27910</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19320</t>
+          <t>20930</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>54569</t>
+          <t>53247</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39671</t>
+          <t>42642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70361</t>
+          <t>66261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>143004</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>132459</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>150695</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,68%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>162690</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>151948</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>173102</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>85,81%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,31%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>157612</t>
+          <t>128294</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146912</t>
+          <t>118063</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165966</t>
+          <t>135274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>320302</t>
+          <t>271298</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>304510</t>
+          <t>258284</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>335200</t>
+          <t>281903</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>86,86%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31117</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23322</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40198</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>18045</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12154</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>26729</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34637</t>
+          <t>16130</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26417</t>
+          <t>10617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45578</t>
+          <t>22821</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>52682</t>
+          <t>47247</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41645</t>
+          <t>37143</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65332</t>
+          <t>58689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>138259</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>129178</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>146054</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>149194</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>140510</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>155085</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>89,21%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>146601</t>
+          <t>150319</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135660</t>
+          <t>143628</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154821</t>
+          <t>155832</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>295795</t>
+          <t>288578</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>283145</t>
+          <t>277136</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>306832</t>
+          <t>298682</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167239</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167239</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167239</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166449</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166449</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166449</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>348477</t>
+          <t>335825</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>348477</t>
+          <t>335825</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348477</t>
+          <t>335825</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>105622</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>90588</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>125160</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15,07%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>103235</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>84008</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>124638</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,53%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,75%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>116838</t>
+          <t>95788</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99617</t>
+          <t>81393</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135313</t>
+          <t>111298</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>220073</t>
+          <t>201409</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>194422</t>
+          <t>176479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>251730</t>
+          <t>226552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>595207</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>575669</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>610241</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>84,93%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>82,14%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>792</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>561382</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>539979</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>580609</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>84,47%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>81,25%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>645134</t>
+          <t>532349</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>626659</t>
+          <t>516839</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>662355</t>
+          <t>546744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1206516</t>
+          <t>1127557</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1174859</t>
+          <t>1102414</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1232167</t>
+          <t>1152487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,72%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664617</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664617</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664617</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628137</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628137</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628137</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426589</t>
+          <t>1328966</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426589</t>
+          <t>1328966</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426589</t>
+          <t>1328966</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
